--- a/data/trans_dic/P33B_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R2-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,22; 18,95</t>
+          <t>13,26; 19,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,66; 25,72</t>
+          <t>20,88; 26,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 21,62</t>
+          <t>17,86; 21,79</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,17</t>
+          <t>11,39; 15,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,2; 24,68</t>
+          <t>20,26; 24,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 18,38</t>
+          <t>16,31; 19,26</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 15,04</t>
+          <t>9,6; 14,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 19,54</t>
+          <t>17,68; 22,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 16,16</t>
+          <t>14,09; 17,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 17,68</t>
+          <t>13,16; 17,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 24,56</t>
+          <t>21,6; 26,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,77; 20,49</t>
+          <t>18,3; 21,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,6</t>
+          <t>12,84; 15,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,4</t>
+          <t>21,33; 23,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,96; 18,27</t>
+          <t>17,55; 19,17</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100349</t>
+          <t>110037</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>171817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256388</t>
+          <t>281854</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83857; 120222</t>
+          <t>91427; 132306</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>139438; 173594</t>
+          <t>152912; 190675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>232940; 283121</t>
+          <t>253934; 309754</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>125727</t>
+          <t>139233</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>215997</t>
+          <t>237945</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341724</t>
+          <t>377178</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55749; 169074</t>
+          <t>119441; 164063</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>193548; 236486</t>
+          <t>216987; 261651</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>232268; 395301</t>
+          <t>345644; 408343</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>93123</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>137164</t>
+          <t>163353</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221830</t>
+          <t>256476</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69502; 105983</t>
+          <t>77098; 114483</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65185; 182338</t>
+          <t>143637; 184431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149333; 264741</t>
+          <t>227545; 287699</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>150328</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>238724</t>
+          <t>267159</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381778</t>
+          <t>417487</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>122533; 163837</t>
+          <t>130329; 171864</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192544; 268307</t>
+          <t>241522; 293452</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>338570; 413701</t>
+          <t>385755; 450844</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>354325; 505079</t>
+          <t>453359; 534440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>596729; 819588</t>
+          <t>796552; 882039</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1064786; 1300366</t>
+          <t>1274926; 1392435</t>
         </is>
       </c>
     </row>
